--- a/ABB_Proyecto/Dashboard_ABB.xlsx
+++ b/ABB_Proyecto/Dashboard_ABB.xlsx
@@ -555,7 +555,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 23/05/2026 22:13</t>
+          <t>Última actualización: 25/05/2026 22:08</t>
         </is>
       </c>
     </row>
